--- a/temp_doc/MAPEL- MTK.xlsx
+++ b/temp_doc/MAPEL- MTK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF217714-7142-CB4D-BCCD-FD040180FB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2A81B4-7C3E-D340-BCFD-DCA821AE73B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19440" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -515,7 +515,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1011</v>
+        <v>1030</v>
       </c>
       <c r="B2">
         <v>1001</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="B4">
         <v>1003</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1014</v>
+        <v>1033</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1015</v>
+        <v>1034</v>
       </c>
       <c r="B6">
         <v>1005</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1016</v>
+        <v>1035</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1017</v>
+        <v>1036</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1018</v>
+        <v>1037</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1019</v>
+        <v>1038</v>
       </c>
       <c r="B10">
         <v>1009</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1020</v>
+        <v>1039</v>
       </c>
       <c r="B11">
         <v>1010</v>
